--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260312_202551.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260312_202551.xlsx
@@ -5156,7 +5156,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5304,7 +5304,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5526,7 +5526,7 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -7586,7 +7586,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7654,7 +7654,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7722,7 +7722,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260312_202551.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260312_202551.xlsx
@@ -5156,7 +5156,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5304,7 +5304,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5526,7 +5526,7 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -7586,7 +7586,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7654,7 +7654,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7722,7 +7722,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260312_202551.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260312_202551.xlsx
@@ -5156,7 +5156,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5304,7 +5304,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5526,7 +5526,7 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260312_202551.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260312_202551.xlsx
@@ -5156,7 +5156,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5304,7 +5304,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5526,7 +5526,7 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5592,7 +5592,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5732,7 +5732,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6114,7 +6114,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6266,7 +6266,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7586,7 +7586,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7654,7 +7654,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7722,7 +7722,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260312_202551.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260312_202551.xlsx
@@ -5156,7 +5156,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5304,7 +5304,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5526,7 +5526,7 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -7586,7 +7586,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7654,7 +7654,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7722,7 +7722,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260312_202551.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260312_202551.xlsx
@@ -5156,7 +5156,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5304,7 +5304,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5526,7 +5526,7 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5592,7 +5592,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5732,7 +5732,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6114,7 +6114,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6266,7 +6266,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260312_202551.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260312_202551.xlsx
@@ -5592,7 +5592,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5732,7 +5732,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6114,7 +6114,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6266,7 +6266,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7586,7 +7586,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7654,7 +7654,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7722,7 +7722,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260312_202551.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260312_202551.xlsx
@@ -7586,7 +7586,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7654,7 +7654,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7722,7 +7722,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260312_202551.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260312_202551.xlsx
@@ -5156,7 +5156,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5304,7 +5304,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5526,7 +5526,7 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5592,7 +5592,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5732,7 +5732,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6114,7 +6114,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6266,7 +6266,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260312_202551.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260312_202551.xlsx
@@ -5156,7 +5156,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5304,7 +5304,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5526,7 +5526,7 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -7586,7 +7586,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7654,7 +7654,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7722,7 +7722,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260312_202551.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260312_202551.xlsx
@@ -5156,7 +5156,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5304,7 +5304,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5526,7 +5526,7 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5592,7 +5592,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5732,7 +5732,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6114,7 +6114,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6266,7 +6266,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7586,7 +7586,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7654,7 +7654,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7722,7 +7722,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260312_202551.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260312_202551.xlsx
@@ -5156,7 +5156,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5304,7 +5304,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5526,7 +5526,7 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260312_202551.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260312_202551.xlsx
@@ -7586,7 +7586,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7654,7 +7654,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7722,7 +7722,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260312_202551.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260312_202551.xlsx
@@ -5592,7 +5592,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5732,7 +5732,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6114,7 +6114,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6266,7 +6266,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7586,7 +7586,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7654,7 +7654,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7722,7 +7722,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260312_202551.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260312_202551.xlsx
@@ -5592,7 +5592,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5732,7 +5732,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6114,7 +6114,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6266,7 +6266,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260312_202551.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260312_202551.xlsx
@@ -5156,7 +5156,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5304,7 +5304,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5526,7 +5526,7 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5592,7 +5592,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5732,7 +5732,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6114,7 +6114,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6266,7 +6266,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7586,7 +7586,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7654,7 +7654,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7722,7 +7722,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260312_202551.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260312_202551.xlsx
@@ -5156,7 +5156,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5304,7 +5304,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5526,7 +5526,7 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5592,7 +5592,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5732,7 +5732,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6114,7 +6114,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6266,7 +6266,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7586,7 +7586,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7654,7 +7654,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7722,7 +7722,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260312_202551.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260312_202551.xlsx
@@ -5592,7 +5592,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5732,7 +5732,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6114,7 +6114,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6266,7 +6266,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260312_202551.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260312_202551.xlsx
@@ -5156,7 +5156,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5304,7 +5304,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5526,7 +5526,7 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5592,7 +5592,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5732,7 +5732,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6114,7 +6114,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6266,7 +6266,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260312_202551.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260312_202551.xlsx
@@ -5156,7 +5156,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5304,7 +5304,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5526,7 +5526,7 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5592,7 +5592,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5732,7 +5732,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6114,7 +6114,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6266,7 +6266,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260312_202551.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260312_202551.xlsx
@@ -5156,7 +5156,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5304,7 +5304,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5526,7 +5526,7 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5592,7 +5592,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5732,7 +5732,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6114,7 +6114,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6266,7 +6266,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7586,7 +7586,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7654,7 +7654,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7722,7 +7722,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260312_202551.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260312_202551.xlsx
@@ -5592,7 +5592,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5732,7 +5732,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6114,7 +6114,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6266,7 +6266,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7586,7 +7586,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7654,7 +7654,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7722,7 +7722,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260312_202551.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260312_202551.xlsx
@@ -5592,7 +5592,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5732,7 +5732,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6114,7 +6114,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6266,7 +6266,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7586,7 +7586,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7654,7 +7654,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7722,7 +7722,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260312_202551.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260312_202551.xlsx
@@ -5156,7 +5156,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5304,7 +5304,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5526,7 +5526,7 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5592,7 +5592,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5732,7 +5732,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6114,7 +6114,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6266,7 +6266,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7586,7 +7586,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7654,7 +7654,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7722,7 +7722,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
